--- a/data/课程知识图谱与数字孪生/用户/学生名单.xlsx
+++ b/data/课程知识图谱与数字孪生/用户/学生名单.xlsx
@@ -5,17 +5,28 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FlutterProjects\knowledge_graph_app\data\CKGDT\用户\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FlutterProjects\knowledge_graph_app\data\课程知识图谱与数字孪生\用户\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{833C8102-4AAF-4B55-92D5-D6D77554C568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{346676CD-681D-4568-824A-C3E104B40A15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="学生名单" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -88,10 +99,11 @@
     <t>2023211985</t>
   </si>
   <si>
+    <t>计算机学院</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>测试学生</t>
-  </si>
-  <si>
-    <t>计算机学院</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -442,6 +454,7 @@
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="17.77734375" customWidth="1"/>
     <col min="3" max="3" width="13.44140625" customWidth="1"/>
     <col min="4" max="4" width="21.6640625" customWidth="1"/>
   </cols>
@@ -480,7 +493,7 @@
         <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
         <v>10</v>
@@ -506,7 +519,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -532,7 +545,7 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D4" t="s">
         <v>10</v>
@@ -558,7 +571,7 @@
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D5" t="s">
         <v>10</v>
@@ -581,10 +594,10 @@
         <v>21</v>
       </c>
       <c r="B6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s">
         <v>22</v>
-      </c>
-      <c r="C6" t="s">
-        <v>23</v>
       </c>
       <c r="D6" t="s">
         <v>10</v>
